--- a/BWI/bestwine_output/bestwine_Austria.xlsx
+++ b/BWI/bestwine_output/bestwine_Austria.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA886"/>
+  <dimension ref="A1:AA889"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -87769,6 +87769,317 @@
       <c r="Z886" s="2" t="inlineStr"/>
       <c r="AA886" s="2" t="inlineStr"/>
     </row>
+    <row r="887">
+      <c r="A887" s="2" t="inlineStr">
+        <is>
+          <t>Wedl Handels-gmbh</t>
+        </is>
+      </c>
+      <c r="B887" s="2" t="inlineStr">
+        <is>
+          <t>Wedl Handels-gmbh</t>
+        </is>
+      </c>
+      <c r="C887" s="2" t="inlineStr">
+        <is>
+          <t>105225</t>
+        </is>
+      </c>
+      <c r="D887" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E887" s="2" t="inlineStr">
+        <is>
+          <t>Mils</t>
+        </is>
+      </c>
+      <c r="F887" s="2" t="inlineStr">
+        <is>
+          <t>Tyrol</t>
+        </is>
+      </c>
+      <c r="G887" s="2" t="inlineStr">
+        <is>
+          <t>1 Leopold-Wedl-Straße</t>
+        </is>
+      </c>
+      <c r="H887" s="2" t="inlineStr">
+        <is>
+          <t>6068</t>
+        </is>
+      </c>
+      <c r="I887" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wedl.com</t>
+        </is>
+      </c>
+      <c r="J887" s="2" t="inlineStr"/>
+      <c r="K887" s="2" t="inlineStr"/>
+      <c r="L887" s="2" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="M887" s="2" t="inlineStr"/>
+      <c r="N887" s="2" t="inlineStr">
+        <is>
+          <t>info@wedl.com</t>
+        </is>
+      </c>
+      <c r="O887" s="2" t="inlineStr">
+        <is>
+          <t>+43 59 3350</t>
+        </is>
+      </c>
+      <c r="P887" s="2" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="Q887" s="2" t="inlineStr">
+        <is>
+          <t>FN314555g</t>
+        </is>
+      </c>
+      <c r="R887" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/handelshauswedl/</t>
+        </is>
+      </c>
+      <c r="S887" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/handelshaus.wedl/</t>
+        </is>
+      </c>
+      <c r="T887" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/handelshaus.wedl/</t>
+        </is>
+      </c>
+      <c r="U887" s="2" t="inlineStr"/>
+      <c r="V887" s="2" t="inlineStr"/>
+      <c r="W887" s="2" t="inlineStr">
+        <is>
+          <t>Neubauer Manuela</t>
+        </is>
+      </c>
+      <c r="X887" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing Manager, Central Purchasing</t>
+        </is>
+      </c>
+      <c r="Y887" s="2" t="inlineStr"/>
+      <c r="Z887" s="2" t="inlineStr"/>
+      <c r="AA887" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/neubauer-manuela-28837896/</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" s="2" t="inlineStr">
+        <is>
+          <t>Wedl Handels-gmbh</t>
+        </is>
+      </c>
+      <c r="B888" s="2" t="inlineStr">
+        <is>
+          <t>Wedl Handels-gmbh</t>
+        </is>
+      </c>
+      <c r="C888" s="2" t="inlineStr">
+        <is>
+          <t>105225</t>
+        </is>
+      </c>
+      <c r="D888" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E888" s="2" t="inlineStr">
+        <is>
+          <t>Mils</t>
+        </is>
+      </c>
+      <c r="F888" s="2" t="inlineStr">
+        <is>
+          <t>Tyrol</t>
+        </is>
+      </c>
+      <c r="G888" s="2" t="inlineStr">
+        <is>
+          <t>1 Leopold-Wedl-Straße</t>
+        </is>
+      </c>
+      <c r="H888" s="2" t="inlineStr">
+        <is>
+          <t>6068</t>
+        </is>
+      </c>
+      <c r="I888" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wedl.com</t>
+        </is>
+      </c>
+      <c r="J888" s="2" t="inlineStr"/>
+      <c r="K888" s="2" t="inlineStr"/>
+      <c r="L888" s="2" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="M888" s="2" t="inlineStr"/>
+      <c r="N888" s="2" t="inlineStr">
+        <is>
+          <t>info@wedl.com</t>
+        </is>
+      </c>
+      <c r="O888" s="2" t="inlineStr">
+        <is>
+          <t>+43 59 3350</t>
+        </is>
+      </c>
+      <c r="P888" s="2" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="Q888" s="2" t="inlineStr">
+        <is>
+          <t>FN314555g</t>
+        </is>
+      </c>
+      <c r="R888" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/handelshauswedl/</t>
+        </is>
+      </c>
+      <c r="S888" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/handelshaus.wedl/</t>
+        </is>
+      </c>
+      <c r="T888" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/handelshaus.wedl/</t>
+        </is>
+      </c>
+      <c r="U888" s="2" t="inlineStr"/>
+      <c r="V888" s="2" t="inlineStr"/>
+      <c r="W888" s="2" t="inlineStr">
+        <is>
+          <t>Klaus Mantl</t>
+        </is>
+      </c>
+      <c r="X888" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y888" s="2" t="inlineStr"/>
+      <c r="Z888" s="2" t="inlineStr"/>
+      <c r="AA888" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/klaus-mantl-b0033a292/</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" s="2" t="inlineStr">
+        <is>
+          <t>Wine-world</t>
+        </is>
+      </c>
+      <c r="B889" s="2" t="inlineStr">
+        <is>
+          <t>Wine-world</t>
+        </is>
+      </c>
+      <c r="C889" s="2" t="inlineStr">
+        <is>
+          <t>89544</t>
+        </is>
+      </c>
+      <c r="D889" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E889" s="2" t="inlineStr">
+        <is>
+          <t>Wien</t>
+        </is>
+      </c>
+      <c r="F889" s="2" t="inlineStr">
+        <is>
+          <t>Wien</t>
+        </is>
+      </c>
+      <c r="G889" s="2" t="inlineStr">
+        <is>
+          <t>124 Laxenburger Straße</t>
+        </is>
+      </c>
+      <c r="H889" s="2" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="I889" s="2" t="inlineStr">
+        <is>
+          <t>https://wine-world.at</t>
+        </is>
+      </c>
+      <c r="J889" s="2" t="inlineStr"/>
+      <c r="K889" s="2" t="inlineStr"/>
+      <c r="L889" s="2" t="inlineStr"/>
+      <c r="M889" s="2" t="inlineStr"/>
+      <c r="N889" s="2" t="inlineStr">
+        <is>
+          <t>orders@wine-world.at</t>
+        </is>
+      </c>
+      <c r="O889" s="2" t="inlineStr"/>
+      <c r="P889" s="2" t="inlineStr"/>
+      <c r="Q889" s="2" t="inlineStr"/>
+      <c r="R889" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wine-world-at/</t>
+        </is>
+      </c>
+      <c r="S889" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/wineworldnew</t>
+        </is>
+      </c>
+      <c r="T889" s="2" t="inlineStr"/>
+      <c r="U889" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/wineworldnew</t>
+        </is>
+      </c>
+      <c r="V889" s="2" t="inlineStr"/>
+      <c r="W889" s="2" t="inlineStr">
+        <is>
+          <t>Katharina Monsberger</t>
+        </is>
+      </c>
+      <c r="X889" s="2" t="inlineStr">
+        <is>
+          <t>Head of Sales</t>
+        </is>
+      </c>
+      <c r="Y889" s="2" t="inlineStr"/>
+      <c r="Z889" s="2" t="inlineStr"/>
+      <c r="AA889" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/katharina-monsberger-bb7bb11a1/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Austria.xlsx
+++ b/BWI/bestwine_output/bestwine_Austria.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA889"/>
+  <dimension ref="A1:AA894"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -88080,6 +88080,519 @@
         </is>
       </c>
     </row>
+    <row r="890">
+      <c r="A890" s="2" t="inlineStr">
+        <is>
+          <t>Laroche Kg</t>
+        </is>
+      </c>
+      <c r="B890" s="2" t="inlineStr">
+        <is>
+          <t>Laroche Kg</t>
+        </is>
+      </c>
+      <c r="C890" s="2" t="inlineStr">
+        <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="D890" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E890" s="2" t="inlineStr">
+        <is>
+          <t>Markt Piesting</t>
+        </is>
+      </c>
+      <c r="F890" s="2" t="inlineStr">
+        <is>
+          <t>Lower Austria</t>
+        </is>
+      </c>
+      <c r="G890" s="2" t="inlineStr">
+        <is>
+          <t>7a Meitzgasse</t>
+        </is>
+      </c>
+      <c r="H890" s="2" t="inlineStr">
+        <is>
+          <t>2753</t>
+        </is>
+      </c>
+      <c r="I890" s="2" t="inlineStr">
+        <is>
+          <t>https://lavinothequelaroche.com</t>
+        </is>
+      </c>
+      <c r="J890" s="2" t="inlineStr"/>
+      <c r="K890" s="2" t="inlineStr"/>
+      <c r="L890" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M890" s="2" t="inlineStr"/>
+      <c r="N890" s="2" t="inlineStr">
+        <is>
+          <t>boutique@laroche.co.at</t>
+        </is>
+      </c>
+      <c r="O890" s="2" t="inlineStr"/>
+      <c r="P890" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q890" s="2" t="inlineStr">
+        <is>
+          <t>ATU57254125</t>
+        </is>
+      </c>
+      <c r="R890" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/laroche/</t>
+        </is>
+      </c>
+      <c r="S890" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/LarocheGenusswelt</t>
+        </is>
+      </c>
+      <c r="T890" s="2" t="inlineStr"/>
+      <c r="U890" s="2" t="inlineStr"/>
+      <c r="V890" s="2" t="inlineStr"/>
+      <c r="W890" s="2" t="inlineStr">
+        <is>
+          <t>Louis-pierre Laroche</t>
+        </is>
+      </c>
+      <c r="X890" s="2" t="inlineStr">
+        <is>
+          <t>Business Owner</t>
+        </is>
+      </c>
+      <c r="Y890" s="2" t="inlineStr"/>
+      <c r="Z890" s="2" t="inlineStr"/>
+      <c r="AA890" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/louis-pierre-laroche-39372114/?originalSubdomain=at</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" s="2" t="inlineStr">
+        <is>
+          <t>Bevertrade Austria Gmbh</t>
+        </is>
+      </c>
+      <c r="B891" s="2" t="inlineStr">
+        <is>
+          <t>Bevertrade Austria Gmbh</t>
+        </is>
+      </c>
+      <c r="C891" s="2" t="inlineStr">
+        <is>
+          <t>88848</t>
+        </is>
+      </c>
+      <c r="D891" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E891" s="2" t="inlineStr">
+        <is>
+          <t>Salzburg</t>
+        </is>
+      </c>
+      <c r="F891" s="2" t="inlineStr">
+        <is>
+          <t>Salzburg</t>
+        </is>
+      </c>
+      <c r="G891" s="2" t="inlineStr">
+        <is>
+          <t>15 Hannakstraße</t>
+        </is>
+      </c>
+      <c r="H891" s="2" t="inlineStr">
+        <is>
+          <t>5023</t>
+        </is>
+      </c>
+      <c r="I891" s="2" t="inlineStr">
+        <is>
+          <t>https://trinklusiv.at, https://www.bevertrade.at, https://www.beverworld.com, https://www.whisky-rum-explorer.at</t>
+        </is>
+      </c>
+      <c r="J891" s="2" t="inlineStr"/>
+      <c r="K891" s="2" t="inlineStr"/>
+      <c r="L891" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M891" s="2" t="inlineStr"/>
+      <c r="N891" s="2" t="inlineStr">
+        <is>
+          <t>info@bevertrade.at</t>
+        </is>
+      </c>
+      <c r="O891" s="2" t="inlineStr">
+        <is>
+          <t>+43 662 251333</t>
+        </is>
+      </c>
+      <c r="P891" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q891" s="2" t="inlineStr">
+        <is>
+          <t>FN471216s</t>
+        </is>
+      </c>
+      <c r="R891" s="2" t="inlineStr"/>
+      <c r="S891" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/trinklusiv</t>
+        </is>
+      </c>
+      <c r="T891" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/trinklusiv/</t>
+        </is>
+      </c>
+      <c r="U891" s="2" t="inlineStr"/>
+      <c r="V891" s="2" t="inlineStr"/>
+      <c r="W891" s="2" t="inlineStr">
+        <is>
+          <t>Robert Weiglhofer</t>
+        </is>
+      </c>
+      <c r="X891" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y891" s="2" t="inlineStr"/>
+      <c r="Z891" s="2" t="inlineStr"/>
+      <c r="AA891" s="2" t="inlineStr"/>
+    </row>
+    <row r="892">
+      <c r="A892" s="2" t="inlineStr">
+        <is>
+          <t>Wedl Handels-gmbh</t>
+        </is>
+      </c>
+      <c r="B892" s="2" t="inlineStr">
+        <is>
+          <t>Wedl Handels-gmbh</t>
+        </is>
+      </c>
+      <c r="C892" s="2" t="inlineStr">
+        <is>
+          <t>105225</t>
+        </is>
+      </c>
+      <c r="D892" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E892" s="2" t="inlineStr">
+        <is>
+          <t>Mils</t>
+        </is>
+      </c>
+      <c r="F892" s="2" t="inlineStr">
+        <is>
+          <t>Tyrol</t>
+        </is>
+      </c>
+      <c r="G892" s="2" t="inlineStr">
+        <is>
+          <t>1 Leopold-Wedl-Straße</t>
+        </is>
+      </c>
+      <c r="H892" s="2" t="inlineStr">
+        <is>
+          <t>6068</t>
+        </is>
+      </c>
+      <c r="I892" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wedl.com</t>
+        </is>
+      </c>
+      <c r="J892" s="2" t="inlineStr"/>
+      <c r="K892" s="2" t="inlineStr"/>
+      <c r="L892" s="2" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="M892" s="2" t="inlineStr"/>
+      <c r="N892" s="2" t="inlineStr">
+        <is>
+          <t>info@wedl.com</t>
+        </is>
+      </c>
+      <c r="O892" s="2" t="inlineStr">
+        <is>
+          <t>+43 59 3350</t>
+        </is>
+      </c>
+      <c r="P892" s="2" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="Q892" s="2" t="inlineStr">
+        <is>
+          <t>FN314555g</t>
+        </is>
+      </c>
+      <c r="R892" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/handelshauswedl/</t>
+        </is>
+      </c>
+      <c r="S892" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/handelshaus.wedl/</t>
+        </is>
+      </c>
+      <c r="T892" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/handelshaus.wedl/</t>
+        </is>
+      </c>
+      <c r="U892" s="2" t="inlineStr"/>
+      <c r="V892" s="2" t="inlineStr"/>
+      <c r="W892" s="2" t="inlineStr">
+        <is>
+          <t>Neubauer Manuela</t>
+        </is>
+      </c>
+      <c r="X892" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing Manager, Central Purchasing</t>
+        </is>
+      </c>
+      <c r="Y892" s="2" t="inlineStr"/>
+      <c r="Z892" s="2" t="inlineStr"/>
+      <c r="AA892" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/neubauer-manuela-28837896/</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" s="2" t="inlineStr">
+        <is>
+          <t>Wedl Handels-gmbh</t>
+        </is>
+      </c>
+      <c r="B893" s="2" t="inlineStr">
+        <is>
+          <t>Wedl Handels-gmbh</t>
+        </is>
+      </c>
+      <c r="C893" s="2" t="inlineStr">
+        <is>
+          <t>105225</t>
+        </is>
+      </c>
+      <c r="D893" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E893" s="2" t="inlineStr">
+        <is>
+          <t>Mils</t>
+        </is>
+      </c>
+      <c r="F893" s="2" t="inlineStr">
+        <is>
+          <t>Tyrol</t>
+        </is>
+      </c>
+      <c r="G893" s="2" t="inlineStr">
+        <is>
+          <t>1 Leopold-Wedl-Straße</t>
+        </is>
+      </c>
+      <c r="H893" s="2" t="inlineStr">
+        <is>
+          <t>6068</t>
+        </is>
+      </c>
+      <c r="I893" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wedl.com</t>
+        </is>
+      </c>
+      <c r="J893" s="2" t="inlineStr"/>
+      <c r="K893" s="2" t="inlineStr"/>
+      <c r="L893" s="2" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="M893" s="2" t="inlineStr"/>
+      <c r="N893" s="2" t="inlineStr">
+        <is>
+          <t>info@wedl.com</t>
+        </is>
+      </c>
+      <c r="O893" s="2" t="inlineStr">
+        <is>
+          <t>+43 59 3350</t>
+        </is>
+      </c>
+      <c r="P893" s="2" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="Q893" s="2" t="inlineStr">
+        <is>
+          <t>FN314555g</t>
+        </is>
+      </c>
+      <c r="R893" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/handelshauswedl/</t>
+        </is>
+      </c>
+      <c r="S893" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/handelshaus.wedl/</t>
+        </is>
+      </c>
+      <c r="T893" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/handelshaus.wedl/</t>
+        </is>
+      </c>
+      <c r="U893" s="2" t="inlineStr"/>
+      <c r="V893" s="2" t="inlineStr"/>
+      <c r="W893" s="2" t="inlineStr">
+        <is>
+          <t>Klaus Mantl</t>
+        </is>
+      </c>
+      <c r="X893" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y893" s="2" t="inlineStr"/>
+      <c r="Z893" s="2" t="inlineStr"/>
+      <c r="AA893" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/klaus-mantl-b0033a292/</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" s="2" t="inlineStr">
+        <is>
+          <t>Wine-world</t>
+        </is>
+      </c>
+      <c r="B894" s="2" t="inlineStr">
+        <is>
+          <t>Wine-world</t>
+        </is>
+      </c>
+      <c r="C894" s="2" t="inlineStr">
+        <is>
+          <t>89544</t>
+        </is>
+      </c>
+      <c r="D894" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E894" s="2" t="inlineStr">
+        <is>
+          <t>Wien</t>
+        </is>
+      </c>
+      <c r="F894" s="2" t="inlineStr">
+        <is>
+          <t>Wien</t>
+        </is>
+      </c>
+      <c r="G894" s="2" t="inlineStr">
+        <is>
+          <t>124 Laxenburger Straße</t>
+        </is>
+      </c>
+      <c r="H894" s="2" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="I894" s="2" t="inlineStr">
+        <is>
+          <t>https://wine-world.at</t>
+        </is>
+      </c>
+      <c r="J894" s="2" t="inlineStr"/>
+      <c r="K894" s="2" t="inlineStr"/>
+      <c r="L894" s="2" t="inlineStr"/>
+      <c r="M894" s="2" t="inlineStr"/>
+      <c r="N894" s="2" t="inlineStr">
+        <is>
+          <t>orders@wine-world.at</t>
+        </is>
+      </c>
+      <c r="O894" s="2" t="inlineStr"/>
+      <c r="P894" s="2" t="inlineStr"/>
+      <c r="Q894" s="2" t="inlineStr"/>
+      <c r="R894" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wine-world-at/</t>
+        </is>
+      </c>
+      <c r="S894" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/wineworldnew</t>
+        </is>
+      </c>
+      <c r="T894" s="2" t="inlineStr"/>
+      <c r="U894" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/wineworldnew</t>
+        </is>
+      </c>
+      <c r="V894" s="2" t="inlineStr"/>
+      <c r="W894" s="2" t="inlineStr">
+        <is>
+          <t>Katharina Monsberger</t>
+        </is>
+      </c>
+      <c r="X894" s="2" t="inlineStr">
+        <is>
+          <t>Head of Sales</t>
+        </is>
+      </c>
+      <c r="Y894" s="2" t="inlineStr"/>
+      <c r="Z894" s="2" t="inlineStr"/>
+      <c r="AA894" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/katharina-monsberger-bb7bb11a1/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Austria.xlsx
+++ b/BWI/bestwine_output/bestwine_Austria.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA894"/>
+  <dimension ref="A1:AA903"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -88593,6 +88593,903 @@
         </is>
       </c>
     </row>
+    <row r="895">
+      <c r="A895" s="2" t="inlineStr">
+        <is>
+          <t>Getränkepool Handels Gmbh</t>
+        </is>
+      </c>
+      <c r="B895" s="2" t="inlineStr">
+        <is>
+          <t>Getränkepool Handels Gmbh</t>
+        </is>
+      </c>
+      <c r="C895" s="2" t="inlineStr">
+        <is>
+          <t>94879</t>
+        </is>
+      </c>
+      <c r="D895" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E895" s="2" t="inlineStr">
+        <is>
+          <t>Salzburg</t>
+        </is>
+      </c>
+      <c r="F895" s="2" t="inlineStr">
+        <is>
+          <t>Salzburg</t>
+        </is>
+      </c>
+      <c r="G895" s="2" t="inlineStr">
+        <is>
+          <t>72 Bachstraße</t>
+        </is>
+      </c>
+      <c r="H895" s="2" t="inlineStr">
+        <is>
+          <t>5023</t>
+        </is>
+      </c>
+      <c r="I895" s="2" t="inlineStr">
+        <is>
+          <t>https://www.getraenkepool.at</t>
+        </is>
+      </c>
+      <c r="J895" s="2" t="inlineStr"/>
+      <c r="K895" s="2" t="inlineStr"/>
+      <c r="L895" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M895" s="2" t="inlineStr"/>
+      <c r="N895" s="2" t="inlineStr">
+        <is>
+          <t>info@getraenkepool.at</t>
+        </is>
+      </c>
+      <c r="O895" s="2" t="inlineStr">
+        <is>
+          <t>+43 662 856735</t>
+        </is>
+      </c>
+      <c r="P895" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q895" s="2" t="inlineStr">
+        <is>
+          <t>FN253093x</t>
+        </is>
+      </c>
+      <c r="R895" s="2" t="inlineStr"/>
+      <c r="S895" s="2" t="inlineStr"/>
+      <c r="T895" s="2" t="inlineStr"/>
+      <c r="U895" s="2" t="inlineStr"/>
+      <c r="V895" s="2" t="inlineStr"/>
+      <c r="W895" s="2" t="inlineStr">
+        <is>
+          <t>Robert Weiglhofer</t>
+        </is>
+      </c>
+      <c r="X895" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y895" s="2" t="inlineStr"/>
+      <c r="Z895" s="2" t="inlineStr"/>
+      <c r="AA895" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/robert-weiglhofer-2828b7a0/</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" s="2" t="inlineStr">
+        <is>
+          <t>Getränkepool Handels Gmbh</t>
+        </is>
+      </c>
+      <c r="B896" s="2" t="inlineStr">
+        <is>
+          <t>Getränkepool Handels Gmbh</t>
+        </is>
+      </c>
+      <c r="C896" s="2" t="inlineStr">
+        <is>
+          <t>94879</t>
+        </is>
+      </c>
+      <c r="D896" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E896" s="2" t="inlineStr">
+        <is>
+          <t>Salzburg</t>
+        </is>
+      </c>
+      <c r="F896" s="2" t="inlineStr">
+        <is>
+          <t>Salzburg</t>
+        </is>
+      </c>
+      <c r="G896" s="2" t="inlineStr">
+        <is>
+          <t>72 Bachstraße</t>
+        </is>
+      </c>
+      <c r="H896" s="2" t="inlineStr">
+        <is>
+          <t>5023</t>
+        </is>
+      </c>
+      <c r="I896" s="2" t="inlineStr">
+        <is>
+          <t>https://www.getraenkepool.at</t>
+        </is>
+      </c>
+      <c r="J896" s="2" t="inlineStr"/>
+      <c r="K896" s="2" t="inlineStr"/>
+      <c r="L896" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M896" s="2" t="inlineStr"/>
+      <c r="N896" s="2" t="inlineStr">
+        <is>
+          <t>info@getraenkepool.at</t>
+        </is>
+      </c>
+      <c r="O896" s="2" t="inlineStr">
+        <is>
+          <t>+43 662 856735</t>
+        </is>
+      </c>
+      <c r="P896" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q896" s="2" t="inlineStr">
+        <is>
+          <t>FN253093x</t>
+        </is>
+      </c>
+      <c r="R896" s="2" t="inlineStr"/>
+      <c r="S896" s="2" t="inlineStr"/>
+      <c r="T896" s="2" t="inlineStr"/>
+      <c r="U896" s="2" t="inlineStr"/>
+      <c r="V896" s="2" t="inlineStr"/>
+      <c r="W896" s="2" t="inlineStr">
+        <is>
+          <t>Markus Schoger</t>
+        </is>
+      </c>
+      <c r="X896" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y896" s="2" t="inlineStr"/>
+      <c r="Z896" s="2" t="inlineStr"/>
+      <c r="AA896" s="2" t="inlineStr"/>
+    </row>
+    <row r="897">
+      <c r="A897" s="2" t="inlineStr">
+        <is>
+          <t>Oliver Hable</t>
+        </is>
+      </c>
+      <c r="B897" s="2" t="inlineStr">
+        <is>
+          <t>Oliver Hable</t>
+        </is>
+      </c>
+      <c r="C897" s="2" t="inlineStr">
+        <is>
+          <t>90393</t>
+        </is>
+      </c>
+      <c r="D897" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E897" s="2" t="inlineStr">
+        <is>
+          <t>Wien</t>
+        </is>
+      </c>
+      <c r="F897" s="2" t="inlineStr">
+        <is>
+          <t>Wien</t>
+        </is>
+      </c>
+      <c r="G897" s="2" t="inlineStr">
+        <is>
+          <t>37 Seidlgasse</t>
+        </is>
+      </c>
+      <c r="H897" s="2" t="inlineStr">
+        <is>
+          <t>1030</t>
+        </is>
+      </c>
+      <c r="I897" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laviepetillante.com</t>
+        </is>
+      </c>
+      <c r="J897" s="2" t="inlineStr"/>
+      <c r="K897" s="2" t="inlineStr"/>
+      <c r="L897" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M897" s="2" t="inlineStr"/>
+      <c r="N897" s="2" t="inlineStr">
+        <is>
+          <t>office@laviepetillante.com</t>
+        </is>
+      </c>
+      <c r="O897" s="2" t="inlineStr"/>
+      <c r="P897" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="Q897" s="2" t="inlineStr">
+        <is>
+          <t>ATU56396778</t>
+        </is>
+      </c>
+      <c r="R897" s="2" t="inlineStr"/>
+      <c r="S897" s="2" t="inlineStr">
+        <is>
+          <t>http://facebook.com/wirliebenchampagner</t>
+        </is>
+      </c>
+      <c r="T897" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dc5vL9xvrIf/</t>
+        </is>
+      </c>
+      <c r="U897" s="2" t="inlineStr"/>
+      <c r="V897" s="2" t="inlineStr"/>
+      <c r="W897" s="2" t="inlineStr">
+        <is>
+          <t>Sabine Hablé</t>
+        </is>
+      </c>
+      <c r="X897" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y897" s="2" t="inlineStr"/>
+      <c r="Z897" s="2" t="inlineStr"/>
+      <c r="AA897" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sabine-habl%C3%A9-294285102/?originalSubdomain=at</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" s="2" t="inlineStr">
+        <is>
+          <t>Roland Harich</t>
+        </is>
+      </c>
+      <c r="B898" s="2" t="inlineStr">
+        <is>
+          <t>Roland Harich</t>
+        </is>
+      </c>
+      <c r="C898" s="2" t="inlineStr">
+        <is>
+          <t>146118</t>
+        </is>
+      </c>
+      <c r="D898" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E898" s="2" t="inlineStr">
+        <is>
+          <t>Mürzzuschlag</t>
+        </is>
+      </c>
+      <c r="F898" s="2" t="inlineStr">
+        <is>
+          <t>Styria</t>
+        </is>
+      </c>
+      <c r="G898" s="2" t="inlineStr">
+        <is>
+          <t>59 Grazer Straße</t>
+        </is>
+      </c>
+      <c r="H898" s="2" t="inlineStr">
+        <is>
+          <t>8680</t>
+        </is>
+      </c>
+      <c r="I898" s="2" t="inlineStr">
+        <is>
+          <t>https://www.getraenke-harich.at</t>
+        </is>
+      </c>
+      <c r="J898" s="2" t="inlineStr"/>
+      <c r="K898" s="2" t="inlineStr"/>
+      <c r="L898" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M898" s="2" t="inlineStr"/>
+      <c r="N898" s="2" t="inlineStr">
+        <is>
+          <t>office@getraenke-harich.at</t>
+        </is>
+      </c>
+      <c r="O898" s="2" t="inlineStr">
+        <is>
+          <t>+43 3852 2685</t>
+        </is>
+      </c>
+      <c r="P898" s="2" t="inlineStr">
+        <is>
+          <t>1920</t>
+        </is>
+      </c>
+      <c r="Q898" s="2" t="inlineStr">
+        <is>
+          <t>FN16837k</t>
+        </is>
+      </c>
+      <c r="R898" s="2" t="inlineStr"/>
+      <c r="S898" s="2" t="inlineStr"/>
+      <c r="T898" s="2" t="inlineStr"/>
+      <c r="U898" s="2" t="inlineStr"/>
+      <c r="V898" s="2" t="inlineStr"/>
+      <c r="W898" s="2" t="inlineStr">
+        <is>
+          <t>Roland Harich</t>
+        </is>
+      </c>
+      <c r="X898" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y898" s="2" t="inlineStr"/>
+      <c r="Z898" s="2" t="inlineStr"/>
+      <c r="AA898" s="2" t="inlineStr"/>
+    </row>
+    <row r="899">
+      <c r="A899" s="2" t="inlineStr">
+        <is>
+          <t>Laroche Kg</t>
+        </is>
+      </c>
+      <c r="B899" s="2" t="inlineStr">
+        <is>
+          <t>Laroche Kg</t>
+        </is>
+      </c>
+      <c r="C899" s="2" t="inlineStr">
+        <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="D899" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E899" s="2" t="inlineStr">
+        <is>
+          <t>Markt Piesting</t>
+        </is>
+      </c>
+      <c r="F899" s="2" t="inlineStr">
+        <is>
+          <t>Lower Austria</t>
+        </is>
+      </c>
+      <c r="G899" s="2" t="inlineStr">
+        <is>
+          <t>7a Meitzgasse</t>
+        </is>
+      </c>
+      <c r="H899" s="2" t="inlineStr">
+        <is>
+          <t>2753</t>
+        </is>
+      </c>
+      <c r="I899" s="2" t="inlineStr">
+        <is>
+          <t>https://lavinothequelaroche.com</t>
+        </is>
+      </c>
+      <c r="J899" s="2" t="inlineStr"/>
+      <c r="K899" s="2" t="inlineStr"/>
+      <c r="L899" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M899" s="2" t="inlineStr"/>
+      <c r="N899" s="2" t="inlineStr">
+        <is>
+          <t>boutique@laroche.co.at</t>
+        </is>
+      </c>
+      <c r="O899" s="2" t="inlineStr"/>
+      <c r="P899" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q899" s="2" t="inlineStr">
+        <is>
+          <t>ATU57254125</t>
+        </is>
+      </c>
+      <c r="R899" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/laroche/</t>
+        </is>
+      </c>
+      <c r="S899" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/LarocheGenusswelt</t>
+        </is>
+      </c>
+      <c r="T899" s="2" t="inlineStr"/>
+      <c r="U899" s="2" t="inlineStr"/>
+      <c r="V899" s="2" t="inlineStr"/>
+      <c r="W899" s="2" t="inlineStr">
+        <is>
+          <t>Louis-pierre Laroche</t>
+        </is>
+      </c>
+      <c r="X899" s="2" t="inlineStr">
+        <is>
+          <t>Business Owner</t>
+        </is>
+      </c>
+      <c r="Y899" s="2" t="inlineStr"/>
+      <c r="Z899" s="2" t="inlineStr"/>
+      <c r="AA899" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/louis-pierre-laroche-39372114/?originalSubdomain=at</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" s="2" t="inlineStr">
+        <is>
+          <t>Bevertrade Austria Gmbh</t>
+        </is>
+      </c>
+      <c r="B900" s="2" t="inlineStr">
+        <is>
+          <t>Bevertrade Austria Gmbh</t>
+        </is>
+      </c>
+      <c r="C900" s="2" t="inlineStr">
+        <is>
+          <t>88848</t>
+        </is>
+      </c>
+      <c r="D900" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E900" s="2" t="inlineStr">
+        <is>
+          <t>Salzburg</t>
+        </is>
+      </c>
+      <c r="F900" s="2" t="inlineStr">
+        <is>
+          <t>Salzburg</t>
+        </is>
+      </c>
+      <c r="G900" s="2" t="inlineStr">
+        <is>
+          <t>15 Hannakstraße</t>
+        </is>
+      </c>
+      <c r="H900" s="2" t="inlineStr">
+        <is>
+          <t>5023</t>
+        </is>
+      </c>
+      <c r="I900" s="2" t="inlineStr">
+        <is>
+          <t>https://trinklusiv.at, https://www.bevertrade.at, https://www.beverworld.com, https://www.whisky-rum-explorer.at</t>
+        </is>
+      </c>
+      <c r="J900" s="2" t="inlineStr"/>
+      <c r="K900" s="2" t="inlineStr"/>
+      <c r="L900" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M900" s="2" t="inlineStr"/>
+      <c r="N900" s="2" t="inlineStr">
+        <is>
+          <t>info@bevertrade.at</t>
+        </is>
+      </c>
+      <c r="O900" s="2" t="inlineStr">
+        <is>
+          <t>+43 662 251333</t>
+        </is>
+      </c>
+      <c r="P900" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q900" s="2" t="inlineStr">
+        <is>
+          <t>FN471216s</t>
+        </is>
+      </c>
+      <c r="R900" s="2" t="inlineStr"/>
+      <c r="S900" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/trinklusiv</t>
+        </is>
+      </c>
+      <c r="T900" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/trinklusiv/</t>
+        </is>
+      </c>
+      <c r="U900" s="2" t="inlineStr"/>
+      <c r="V900" s="2" t="inlineStr"/>
+      <c r="W900" s="2" t="inlineStr">
+        <is>
+          <t>Robert Weiglhofer</t>
+        </is>
+      </c>
+      <c r="X900" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y900" s="2" t="inlineStr"/>
+      <c r="Z900" s="2" t="inlineStr"/>
+      <c r="AA900" s="2" t="inlineStr"/>
+    </row>
+    <row r="901">
+      <c r="A901" s="2" t="inlineStr">
+        <is>
+          <t>Wedl Handels-gmbh</t>
+        </is>
+      </c>
+      <c r="B901" s="2" t="inlineStr">
+        <is>
+          <t>Wedl Handels-gmbh</t>
+        </is>
+      </c>
+      <c r="C901" s="2" t="inlineStr">
+        <is>
+          <t>105225</t>
+        </is>
+      </c>
+      <c r="D901" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E901" s="2" t="inlineStr">
+        <is>
+          <t>Mils</t>
+        </is>
+      </c>
+      <c r="F901" s="2" t="inlineStr">
+        <is>
+          <t>Tyrol</t>
+        </is>
+      </c>
+      <c r="G901" s="2" t="inlineStr">
+        <is>
+          <t>1 Leopold-Wedl-Straße</t>
+        </is>
+      </c>
+      <c r="H901" s="2" t="inlineStr">
+        <is>
+          <t>6068</t>
+        </is>
+      </c>
+      <c r="I901" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wedl.com</t>
+        </is>
+      </c>
+      <c r="J901" s="2" t="inlineStr"/>
+      <c r="K901" s="2" t="inlineStr"/>
+      <c r="L901" s="2" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="M901" s="2" t="inlineStr"/>
+      <c r="N901" s="2" t="inlineStr">
+        <is>
+          <t>info@wedl.com</t>
+        </is>
+      </c>
+      <c r="O901" s="2" t="inlineStr">
+        <is>
+          <t>+43 59 3350</t>
+        </is>
+      </c>
+      <c r="P901" s="2" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="Q901" s="2" t="inlineStr">
+        <is>
+          <t>FN314555g</t>
+        </is>
+      </c>
+      <c r="R901" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/handelshauswedl/</t>
+        </is>
+      </c>
+      <c r="S901" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/handelshaus.wedl/</t>
+        </is>
+      </c>
+      <c r="T901" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/handelshaus.wedl/</t>
+        </is>
+      </c>
+      <c r="U901" s="2" t="inlineStr"/>
+      <c r="V901" s="2" t="inlineStr"/>
+      <c r="W901" s="2" t="inlineStr">
+        <is>
+          <t>Neubauer Manuela</t>
+        </is>
+      </c>
+      <c r="X901" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing Manager, Central Purchasing</t>
+        </is>
+      </c>
+      <c r="Y901" s="2" t="inlineStr"/>
+      <c r="Z901" s="2" t="inlineStr"/>
+      <c r="AA901" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/neubauer-manuela-28837896/</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" s="2" t="inlineStr">
+        <is>
+          <t>Wedl Handels-gmbh</t>
+        </is>
+      </c>
+      <c r="B902" s="2" t="inlineStr">
+        <is>
+          <t>Wedl Handels-gmbh</t>
+        </is>
+      </c>
+      <c r="C902" s="2" t="inlineStr">
+        <is>
+          <t>105225</t>
+        </is>
+      </c>
+      <c r="D902" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E902" s="2" t="inlineStr">
+        <is>
+          <t>Mils</t>
+        </is>
+      </c>
+      <c r="F902" s="2" t="inlineStr">
+        <is>
+          <t>Tyrol</t>
+        </is>
+      </c>
+      <c r="G902" s="2" t="inlineStr">
+        <is>
+          <t>1 Leopold-Wedl-Straße</t>
+        </is>
+      </c>
+      <c r="H902" s="2" t="inlineStr">
+        <is>
+          <t>6068</t>
+        </is>
+      </c>
+      <c r="I902" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wedl.com</t>
+        </is>
+      </c>
+      <c r="J902" s="2" t="inlineStr"/>
+      <c r="K902" s="2" t="inlineStr"/>
+      <c r="L902" s="2" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="M902" s="2" t="inlineStr"/>
+      <c r="N902" s="2" t="inlineStr">
+        <is>
+          <t>info@wedl.com</t>
+        </is>
+      </c>
+      <c r="O902" s="2" t="inlineStr">
+        <is>
+          <t>+43 59 3350</t>
+        </is>
+      </c>
+      <c r="P902" s="2" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="Q902" s="2" t="inlineStr">
+        <is>
+          <t>FN314555g</t>
+        </is>
+      </c>
+      <c r="R902" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/handelshauswedl/</t>
+        </is>
+      </c>
+      <c r="S902" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/handelshaus.wedl/</t>
+        </is>
+      </c>
+      <c r="T902" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/handelshaus.wedl/</t>
+        </is>
+      </c>
+      <c r="U902" s="2" t="inlineStr"/>
+      <c r="V902" s="2" t="inlineStr"/>
+      <c r="W902" s="2" t="inlineStr">
+        <is>
+          <t>Klaus Mantl</t>
+        </is>
+      </c>
+      <c r="X902" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y902" s="2" t="inlineStr"/>
+      <c r="Z902" s="2" t="inlineStr"/>
+      <c r="AA902" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/klaus-mantl-b0033a292/</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" s="2" t="inlineStr">
+        <is>
+          <t>Wine-world</t>
+        </is>
+      </c>
+      <c r="B903" s="2" t="inlineStr">
+        <is>
+          <t>Wine-world</t>
+        </is>
+      </c>
+      <c r="C903" s="2" t="inlineStr">
+        <is>
+          <t>89544</t>
+        </is>
+      </c>
+      <c r="D903" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E903" s="2" t="inlineStr">
+        <is>
+          <t>Wien</t>
+        </is>
+      </c>
+      <c r="F903" s="2" t="inlineStr">
+        <is>
+          <t>Wien</t>
+        </is>
+      </c>
+      <c r="G903" s="2" t="inlineStr">
+        <is>
+          <t>124 Laxenburger Straße</t>
+        </is>
+      </c>
+      <c r="H903" s="2" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="I903" s="2" t="inlineStr">
+        <is>
+          <t>https://wine-world.at</t>
+        </is>
+      </c>
+      <c r="J903" s="2" t="inlineStr"/>
+      <c r="K903" s="2" t="inlineStr"/>
+      <c r="L903" s="2" t="inlineStr"/>
+      <c r="M903" s="2" t="inlineStr"/>
+      <c r="N903" s="2" t="inlineStr">
+        <is>
+          <t>orders@wine-world.at</t>
+        </is>
+      </c>
+      <c r="O903" s="2" t="inlineStr"/>
+      <c r="P903" s="2" t="inlineStr"/>
+      <c r="Q903" s="2" t="inlineStr"/>
+      <c r="R903" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wine-world-at/</t>
+        </is>
+      </c>
+      <c r="S903" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/wineworldnew</t>
+        </is>
+      </c>
+      <c r="T903" s="2" t="inlineStr"/>
+      <c r="U903" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/wineworldnew</t>
+        </is>
+      </c>
+      <c r="V903" s="2" t="inlineStr"/>
+      <c r="W903" s="2" t="inlineStr">
+        <is>
+          <t>Katharina Monsberger</t>
+        </is>
+      </c>
+      <c r="X903" s="2" t="inlineStr">
+        <is>
+          <t>Head of Sales</t>
+        </is>
+      </c>
+      <c r="Y903" s="2" t="inlineStr"/>
+      <c r="Z903" s="2" t="inlineStr"/>
+      <c r="AA903" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/katharina-monsberger-bb7bb11a1/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Austria.xlsx
+++ b/BWI/bestwine_output/bestwine_Austria.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA903"/>
+  <dimension ref="A1:AA914"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -89490,6 +89490,1073 @@
         </is>
       </c>
     </row>
+    <row r="904">
+      <c r="A904" s="2" t="inlineStr">
+        <is>
+          <t>MIWI Import &amp; Vertriebs GmbH</t>
+        </is>
+      </c>
+      <c r="B904" s="2" t="inlineStr"/>
+      <c r="C904" s="2" t="inlineStr">
+        <is>
+          <t>168941</t>
+        </is>
+      </c>
+      <c r="D904" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E904" s="2" t="inlineStr">
+        <is>
+          <t>Wien</t>
+        </is>
+      </c>
+      <c r="F904" s="2" t="inlineStr">
+        <is>
+          <t>Vienna</t>
+        </is>
+      </c>
+      <c r="G904" s="2" t="inlineStr">
+        <is>
+          <t>Seitenstettengasse 5</t>
+        </is>
+      </c>
+      <c r="H904" s="2" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="I904" s="2" t="inlineStr">
+        <is>
+          <t>https://miwi.at</t>
+        </is>
+      </c>
+      <c r="J904" s="2" t="inlineStr"/>
+      <c r="K904" s="2" t="inlineStr"/>
+      <c r="L904" s="2" t="inlineStr"/>
+      <c r="M904" s="2" t="inlineStr"/>
+      <c r="N904" s="2" t="inlineStr">
+        <is>
+          <t>wimmer@miwi.at</t>
+        </is>
+      </c>
+      <c r="O904" s="2" t="inlineStr"/>
+      <c r="P904" s="2" t="inlineStr"/>
+      <c r="Q904" s="2" t="inlineStr"/>
+      <c r="R904" s="2" t="inlineStr"/>
+      <c r="S904" s="2" t="inlineStr"/>
+      <c r="T904" s="2" t="inlineStr"/>
+      <c r="U904" s="2" t="inlineStr"/>
+      <c r="V904" s="2" t="inlineStr"/>
+      <c r="W904" s="2" t="inlineStr">
+        <is>
+          <t>Michael Wimmer</t>
+        </is>
+      </c>
+      <c r="X904" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y904" s="2" t="inlineStr"/>
+      <c r="Z904" s="2" t="inlineStr"/>
+      <c r="AA904" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/michael-wimmer-65504890/</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nix Drin </t>
+        </is>
+      </c>
+      <c r="B905" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nix Drin </t>
+        </is>
+      </c>
+      <c r="C905" s="2" t="inlineStr">
+        <is>
+          <t>90388</t>
+        </is>
+      </c>
+      <c r="D905" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E905" s="2" t="inlineStr">
+        <is>
+          <t>Breitenbach</t>
+        </is>
+      </c>
+      <c r="F905" s="2" t="inlineStr">
+        <is>
+          <t>Tyrol</t>
+        </is>
+      </c>
+      <c r="G905" s="2" t="inlineStr">
+        <is>
+          <t>Dorf 6, 1. Stock</t>
+        </is>
+      </c>
+      <c r="H905" s="2" t="inlineStr">
+        <is>
+          <t>6252</t>
+        </is>
+      </c>
+      <c r="I905" s="2" t="inlineStr">
+        <is>
+          <t>https://www.claudias-saftladen.at, https://www.nix-drin.at</t>
+        </is>
+      </c>
+      <c r="J905" s="2" t="inlineStr"/>
+      <c r="K905" s="2" t="inlineStr"/>
+      <c r="L905" s="2" t="inlineStr"/>
+      <c r="M905" s="2" t="inlineStr"/>
+      <c r="N905" s="2" t="inlineStr">
+        <is>
+          <t>info@nix-drin.at</t>
+        </is>
+      </c>
+      <c r="O905" s="2" t="inlineStr">
+        <is>
+          <t>+43 5338 21010</t>
+        </is>
+      </c>
+      <c r="P905" s="2" t="inlineStr"/>
+      <c r="Q905" s="2" t="inlineStr"/>
+      <c r="R905" s="2" t="inlineStr"/>
+      <c r="S905" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ClaudiasSaftladen/</t>
+        </is>
+      </c>
+      <c r="T905" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nixdrin_official</t>
+        </is>
+      </c>
+      <c r="U905" s="2" t="inlineStr"/>
+      <c r="V905" s="2" t="inlineStr"/>
+      <c r="W905" s="2" t="inlineStr">
+        <is>
+          <t>Claudia Schwarzenbacher</t>
+        </is>
+      </c>
+      <c r="X905" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y905" s="2" t="inlineStr"/>
+      <c r="Z905" s="2" t="inlineStr"/>
+      <c r="AA905" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/claudia-schwarzenbacher-a960b8277/</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" s="2" t="inlineStr">
+        <is>
+          <t>Getränkepool Handels Gmbh</t>
+        </is>
+      </c>
+      <c r="B906" s="2" t="inlineStr">
+        <is>
+          <t>Getränkepool Handels Gmbh</t>
+        </is>
+      </c>
+      <c r="C906" s="2" t="inlineStr">
+        <is>
+          <t>94879</t>
+        </is>
+      </c>
+      <c r="D906" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E906" s="2" t="inlineStr">
+        <is>
+          <t>Salzburg</t>
+        </is>
+      </c>
+      <c r="F906" s="2" t="inlineStr">
+        <is>
+          <t>Salzburg</t>
+        </is>
+      </c>
+      <c r="G906" s="2" t="inlineStr">
+        <is>
+          <t>72 Bachstraße</t>
+        </is>
+      </c>
+      <c r="H906" s="2" t="inlineStr">
+        <is>
+          <t>5023</t>
+        </is>
+      </c>
+      <c r="I906" s="2" t="inlineStr">
+        <is>
+          <t>https://www.getraenkepool.at</t>
+        </is>
+      </c>
+      <c r="J906" s="2" t="inlineStr"/>
+      <c r="K906" s="2" t="inlineStr"/>
+      <c r="L906" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M906" s="2" t="inlineStr"/>
+      <c r="N906" s="2" t="inlineStr">
+        <is>
+          <t>info@getraenkepool.at</t>
+        </is>
+      </c>
+      <c r="O906" s="2" t="inlineStr">
+        <is>
+          <t>+43 662 856735</t>
+        </is>
+      </c>
+      <c r="P906" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q906" s="2" t="inlineStr">
+        <is>
+          <t>FN253093x</t>
+        </is>
+      </c>
+      <c r="R906" s="2" t="inlineStr"/>
+      <c r="S906" s="2" t="inlineStr"/>
+      <c r="T906" s="2" t="inlineStr"/>
+      <c r="U906" s="2" t="inlineStr"/>
+      <c r="V906" s="2" t="inlineStr"/>
+      <c r="W906" s="2" t="inlineStr">
+        <is>
+          <t>Robert Weiglhofer</t>
+        </is>
+      </c>
+      <c r="X906" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y906" s="2" t="inlineStr"/>
+      <c r="Z906" s="2" t="inlineStr"/>
+      <c r="AA906" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/robert-weiglhofer-2828b7a0/</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" s="2" t="inlineStr">
+        <is>
+          <t>Getränkepool Handels Gmbh</t>
+        </is>
+      </c>
+      <c r="B907" s="2" t="inlineStr">
+        <is>
+          <t>Getränkepool Handels Gmbh</t>
+        </is>
+      </c>
+      <c r="C907" s="2" t="inlineStr">
+        <is>
+          <t>94879</t>
+        </is>
+      </c>
+      <c r="D907" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E907" s="2" t="inlineStr">
+        <is>
+          <t>Salzburg</t>
+        </is>
+      </c>
+      <c r="F907" s="2" t="inlineStr">
+        <is>
+          <t>Salzburg</t>
+        </is>
+      </c>
+      <c r="G907" s="2" t="inlineStr">
+        <is>
+          <t>72 Bachstraße</t>
+        </is>
+      </c>
+      <c r="H907" s="2" t="inlineStr">
+        <is>
+          <t>5023</t>
+        </is>
+      </c>
+      <c r="I907" s="2" t="inlineStr">
+        <is>
+          <t>https://www.getraenkepool.at</t>
+        </is>
+      </c>
+      <c r="J907" s="2" t="inlineStr"/>
+      <c r="K907" s="2" t="inlineStr"/>
+      <c r="L907" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M907" s="2" t="inlineStr"/>
+      <c r="N907" s="2" t="inlineStr">
+        <is>
+          <t>info@getraenkepool.at</t>
+        </is>
+      </c>
+      <c r="O907" s="2" t="inlineStr">
+        <is>
+          <t>+43 662 856735</t>
+        </is>
+      </c>
+      <c r="P907" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q907" s="2" t="inlineStr">
+        <is>
+          <t>FN253093x</t>
+        </is>
+      </c>
+      <c r="R907" s="2" t="inlineStr"/>
+      <c r="S907" s="2" t="inlineStr"/>
+      <c r="T907" s="2" t="inlineStr"/>
+      <c r="U907" s="2" t="inlineStr"/>
+      <c r="V907" s="2" t="inlineStr"/>
+      <c r="W907" s="2" t="inlineStr">
+        <is>
+          <t>Markus Schoger</t>
+        </is>
+      </c>
+      <c r="X907" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y907" s="2" t="inlineStr"/>
+      <c r="Z907" s="2" t="inlineStr"/>
+      <c r="AA907" s="2" t="inlineStr"/>
+    </row>
+    <row r="908">
+      <c r="A908" s="2" t="inlineStr">
+        <is>
+          <t>Oliver Hable</t>
+        </is>
+      </c>
+      <c r="B908" s="2" t="inlineStr">
+        <is>
+          <t>Oliver Hable</t>
+        </is>
+      </c>
+      <c r="C908" s="2" t="inlineStr">
+        <is>
+          <t>90393</t>
+        </is>
+      </c>
+      <c r="D908" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E908" s="2" t="inlineStr">
+        <is>
+          <t>Wien</t>
+        </is>
+      </c>
+      <c r="F908" s="2" t="inlineStr">
+        <is>
+          <t>Wien</t>
+        </is>
+      </c>
+      <c r="G908" s="2" t="inlineStr">
+        <is>
+          <t>37 Seidlgasse</t>
+        </is>
+      </c>
+      <c r="H908" s="2" t="inlineStr">
+        <is>
+          <t>1030</t>
+        </is>
+      </c>
+      <c r="I908" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laviepetillante.com</t>
+        </is>
+      </c>
+      <c r="J908" s="2" t="inlineStr"/>
+      <c r="K908" s="2" t="inlineStr"/>
+      <c r="L908" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M908" s="2" t="inlineStr"/>
+      <c r="N908" s="2" t="inlineStr">
+        <is>
+          <t>office@laviepetillante.com</t>
+        </is>
+      </c>
+      <c r="O908" s="2" t="inlineStr"/>
+      <c r="P908" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="Q908" s="2" t="inlineStr">
+        <is>
+          <t>ATU56396778</t>
+        </is>
+      </c>
+      <c r="R908" s="2" t="inlineStr"/>
+      <c r="S908" s="2" t="inlineStr">
+        <is>
+          <t>http://facebook.com/wirliebenchampagner</t>
+        </is>
+      </c>
+      <c r="T908" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dc5vL9xvrIf/</t>
+        </is>
+      </c>
+      <c r="U908" s="2" t="inlineStr"/>
+      <c r="V908" s="2" t="inlineStr"/>
+      <c r="W908" s="2" t="inlineStr">
+        <is>
+          <t>Sabine Hablé</t>
+        </is>
+      </c>
+      <c r="X908" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y908" s="2" t="inlineStr"/>
+      <c r="Z908" s="2" t="inlineStr"/>
+      <c r="AA908" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sabine-habl%C3%A9-294285102/?originalSubdomain=at</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" s="2" t="inlineStr">
+        <is>
+          <t>Roland Harich</t>
+        </is>
+      </c>
+      <c r="B909" s="2" t="inlineStr">
+        <is>
+          <t>Roland Harich</t>
+        </is>
+      </c>
+      <c r="C909" s="2" t="inlineStr">
+        <is>
+          <t>146118</t>
+        </is>
+      </c>
+      <c r="D909" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E909" s="2" t="inlineStr">
+        <is>
+          <t>Mürzzuschlag</t>
+        </is>
+      </c>
+      <c r="F909" s="2" t="inlineStr">
+        <is>
+          <t>Styria</t>
+        </is>
+      </c>
+      <c r="G909" s="2" t="inlineStr">
+        <is>
+          <t>59 Grazer Straße</t>
+        </is>
+      </c>
+      <c r="H909" s="2" t="inlineStr">
+        <is>
+          <t>8680</t>
+        </is>
+      </c>
+      <c r="I909" s="2" t="inlineStr">
+        <is>
+          <t>https://www.getraenke-harich.at</t>
+        </is>
+      </c>
+      <c r="J909" s="2" t="inlineStr"/>
+      <c r="K909" s="2" t="inlineStr"/>
+      <c r="L909" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M909" s="2" t="inlineStr"/>
+      <c r="N909" s="2" t="inlineStr">
+        <is>
+          <t>office@getraenke-harich.at</t>
+        </is>
+      </c>
+      <c r="O909" s="2" t="inlineStr">
+        <is>
+          <t>+43 3852 2685</t>
+        </is>
+      </c>
+      <c r="P909" s="2" t="inlineStr">
+        <is>
+          <t>1920</t>
+        </is>
+      </c>
+      <c r="Q909" s="2" t="inlineStr">
+        <is>
+          <t>FN16837k</t>
+        </is>
+      </c>
+      <c r="R909" s="2" t="inlineStr"/>
+      <c r="S909" s="2" t="inlineStr"/>
+      <c r="T909" s="2" t="inlineStr"/>
+      <c r="U909" s="2" t="inlineStr"/>
+      <c r="V909" s="2" t="inlineStr"/>
+      <c r="W909" s="2" t="inlineStr">
+        <is>
+          <t>Roland Harich</t>
+        </is>
+      </c>
+      <c r="X909" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y909" s="2" t="inlineStr"/>
+      <c r="Z909" s="2" t="inlineStr"/>
+      <c r="AA909" s="2" t="inlineStr"/>
+    </row>
+    <row r="910">
+      <c r="A910" s="2" t="inlineStr">
+        <is>
+          <t>Laroche Kg</t>
+        </is>
+      </c>
+      <c r="B910" s="2" t="inlineStr">
+        <is>
+          <t>Laroche Kg</t>
+        </is>
+      </c>
+      <c r="C910" s="2" t="inlineStr">
+        <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="D910" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E910" s="2" t="inlineStr">
+        <is>
+          <t>Markt Piesting</t>
+        </is>
+      </c>
+      <c r="F910" s="2" t="inlineStr">
+        <is>
+          <t>Lower Austria</t>
+        </is>
+      </c>
+      <c r="G910" s="2" t="inlineStr">
+        <is>
+          <t>7a Meitzgasse</t>
+        </is>
+      </c>
+      <c r="H910" s="2" t="inlineStr">
+        <is>
+          <t>2753</t>
+        </is>
+      </c>
+      <c r="I910" s="2" t="inlineStr">
+        <is>
+          <t>https://lavinothequelaroche.com</t>
+        </is>
+      </c>
+      <c r="J910" s="2" t="inlineStr"/>
+      <c r="K910" s="2" t="inlineStr"/>
+      <c r="L910" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M910" s="2" t="inlineStr"/>
+      <c r="N910" s="2" t="inlineStr">
+        <is>
+          <t>boutique@laroche.co.at</t>
+        </is>
+      </c>
+      <c r="O910" s="2" t="inlineStr"/>
+      <c r="P910" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q910" s="2" t="inlineStr">
+        <is>
+          <t>ATU57254125</t>
+        </is>
+      </c>
+      <c r="R910" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/laroche/</t>
+        </is>
+      </c>
+      <c r="S910" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/LarocheGenusswelt</t>
+        </is>
+      </c>
+      <c r="T910" s="2" t="inlineStr"/>
+      <c r="U910" s="2" t="inlineStr"/>
+      <c r="V910" s="2" t="inlineStr"/>
+      <c r="W910" s="2" t="inlineStr">
+        <is>
+          <t>Louis-pierre Laroche</t>
+        </is>
+      </c>
+      <c r="X910" s="2" t="inlineStr">
+        <is>
+          <t>Business Owner</t>
+        </is>
+      </c>
+      <c r="Y910" s="2" t="inlineStr"/>
+      <c r="Z910" s="2" t="inlineStr"/>
+      <c r="AA910" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/louis-pierre-laroche-39372114/?originalSubdomain=at</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" s="2" t="inlineStr">
+        <is>
+          <t>Bevertrade Austria Gmbh</t>
+        </is>
+      </c>
+      <c r="B911" s="2" t="inlineStr">
+        <is>
+          <t>Bevertrade Austria Gmbh</t>
+        </is>
+      </c>
+      <c r="C911" s="2" t="inlineStr">
+        <is>
+          <t>88848</t>
+        </is>
+      </c>
+      <c r="D911" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E911" s="2" t="inlineStr">
+        <is>
+          <t>Salzburg</t>
+        </is>
+      </c>
+      <c r="F911" s="2" t="inlineStr">
+        <is>
+          <t>Salzburg</t>
+        </is>
+      </c>
+      <c r="G911" s="2" t="inlineStr">
+        <is>
+          <t>15 Hannakstraße</t>
+        </is>
+      </c>
+      <c r="H911" s="2" t="inlineStr">
+        <is>
+          <t>5023</t>
+        </is>
+      </c>
+      <c r="I911" s="2" t="inlineStr">
+        <is>
+          <t>https://trinklusiv.at, https://www.bevertrade.at, https://www.beverworld.com, https://www.whisky-rum-explorer.at</t>
+        </is>
+      </c>
+      <c r="J911" s="2" t="inlineStr"/>
+      <c r="K911" s="2" t="inlineStr"/>
+      <c r="L911" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M911" s="2" t="inlineStr"/>
+      <c r="N911" s="2" t="inlineStr">
+        <is>
+          <t>info@bevertrade.at</t>
+        </is>
+      </c>
+      <c r="O911" s="2" t="inlineStr">
+        <is>
+          <t>+43 662 251333</t>
+        </is>
+      </c>
+      <c r="P911" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q911" s="2" t="inlineStr">
+        <is>
+          <t>FN471216s</t>
+        </is>
+      </c>
+      <c r="R911" s="2" t="inlineStr"/>
+      <c r="S911" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/trinklusiv</t>
+        </is>
+      </c>
+      <c r="T911" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/trinklusiv/</t>
+        </is>
+      </c>
+      <c r="U911" s="2" t="inlineStr"/>
+      <c r="V911" s="2" t="inlineStr"/>
+      <c r="W911" s="2" t="inlineStr">
+        <is>
+          <t>Robert Weiglhofer</t>
+        </is>
+      </c>
+      <c r="X911" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y911" s="2" t="inlineStr"/>
+      <c r="Z911" s="2" t="inlineStr"/>
+      <c r="AA911" s="2" t="inlineStr"/>
+    </row>
+    <row r="912">
+      <c r="A912" s="2" t="inlineStr">
+        <is>
+          <t>Wedl Handels-gmbh</t>
+        </is>
+      </c>
+      <c r="B912" s="2" t="inlineStr">
+        <is>
+          <t>Wedl Handels-gmbh</t>
+        </is>
+      </c>
+      <c r="C912" s="2" t="inlineStr">
+        <is>
+          <t>105225</t>
+        </is>
+      </c>
+      <c r="D912" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E912" s="2" t="inlineStr">
+        <is>
+          <t>Mils</t>
+        </is>
+      </c>
+      <c r="F912" s="2" t="inlineStr">
+        <is>
+          <t>Tyrol</t>
+        </is>
+      </c>
+      <c r="G912" s="2" t="inlineStr">
+        <is>
+          <t>1 Leopold-Wedl-Straße</t>
+        </is>
+      </c>
+      <c r="H912" s="2" t="inlineStr">
+        <is>
+          <t>6068</t>
+        </is>
+      </c>
+      <c r="I912" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wedl.com</t>
+        </is>
+      </c>
+      <c r="J912" s="2" t="inlineStr"/>
+      <c r="K912" s="2" t="inlineStr"/>
+      <c r="L912" s="2" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="M912" s="2" t="inlineStr"/>
+      <c r="N912" s="2" t="inlineStr">
+        <is>
+          <t>info@wedl.com</t>
+        </is>
+      </c>
+      <c r="O912" s="2" t="inlineStr">
+        <is>
+          <t>+43 59 3350</t>
+        </is>
+      </c>
+      <c r="P912" s="2" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="Q912" s="2" t="inlineStr">
+        <is>
+          <t>FN314555g</t>
+        </is>
+      </c>
+      <c r="R912" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/handelshauswedl/</t>
+        </is>
+      </c>
+      <c r="S912" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/handelshaus.wedl/</t>
+        </is>
+      </c>
+      <c r="T912" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/handelshaus.wedl/</t>
+        </is>
+      </c>
+      <c r="U912" s="2" t="inlineStr"/>
+      <c r="V912" s="2" t="inlineStr"/>
+      <c r="W912" s="2" t="inlineStr">
+        <is>
+          <t>Neubauer Manuela</t>
+        </is>
+      </c>
+      <c r="X912" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing Manager, Central Purchasing</t>
+        </is>
+      </c>
+      <c r="Y912" s="2" t="inlineStr"/>
+      <c r="Z912" s="2" t="inlineStr"/>
+      <c r="AA912" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/neubauer-manuela-28837896/</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" s="2" t="inlineStr">
+        <is>
+          <t>Wedl Handels-gmbh</t>
+        </is>
+      </c>
+      <c r="B913" s="2" t="inlineStr">
+        <is>
+          <t>Wedl Handels-gmbh</t>
+        </is>
+      </c>
+      <c r="C913" s="2" t="inlineStr">
+        <is>
+          <t>105225</t>
+        </is>
+      </c>
+      <c r="D913" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E913" s="2" t="inlineStr">
+        <is>
+          <t>Mils</t>
+        </is>
+      </c>
+      <c r="F913" s="2" t="inlineStr">
+        <is>
+          <t>Tyrol</t>
+        </is>
+      </c>
+      <c r="G913" s="2" t="inlineStr">
+        <is>
+          <t>1 Leopold-Wedl-Straße</t>
+        </is>
+      </c>
+      <c r="H913" s="2" t="inlineStr">
+        <is>
+          <t>6068</t>
+        </is>
+      </c>
+      <c r="I913" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wedl.com</t>
+        </is>
+      </c>
+      <c r="J913" s="2" t="inlineStr"/>
+      <c r="K913" s="2" t="inlineStr"/>
+      <c r="L913" s="2" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="M913" s="2" t="inlineStr"/>
+      <c r="N913" s="2" t="inlineStr">
+        <is>
+          <t>info@wedl.com</t>
+        </is>
+      </c>
+      <c r="O913" s="2" t="inlineStr">
+        <is>
+          <t>+43 59 3350</t>
+        </is>
+      </c>
+      <c r="P913" s="2" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="Q913" s="2" t="inlineStr">
+        <is>
+          <t>FN314555g</t>
+        </is>
+      </c>
+      <c r="R913" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/handelshauswedl/</t>
+        </is>
+      </c>
+      <c r="S913" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/handelshaus.wedl/</t>
+        </is>
+      </c>
+      <c r="T913" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/handelshaus.wedl/</t>
+        </is>
+      </c>
+      <c r="U913" s="2" t="inlineStr"/>
+      <c r="V913" s="2" t="inlineStr"/>
+      <c r="W913" s="2" t="inlineStr">
+        <is>
+          <t>Klaus Mantl</t>
+        </is>
+      </c>
+      <c r="X913" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y913" s="2" t="inlineStr"/>
+      <c r="Z913" s="2" t="inlineStr"/>
+      <c r="AA913" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/klaus-mantl-b0033a292/</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" s="2" t="inlineStr">
+        <is>
+          <t>Wine-world</t>
+        </is>
+      </c>
+      <c r="B914" s="2" t="inlineStr">
+        <is>
+          <t>Wine-world</t>
+        </is>
+      </c>
+      <c r="C914" s="2" t="inlineStr">
+        <is>
+          <t>89544</t>
+        </is>
+      </c>
+      <c r="D914" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E914" s="2" t="inlineStr">
+        <is>
+          <t>Wien</t>
+        </is>
+      </c>
+      <c r="F914" s="2" t="inlineStr">
+        <is>
+          <t>Wien</t>
+        </is>
+      </c>
+      <c r="G914" s="2" t="inlineStr">
+        <is>
+          <t>124 Laxenburger Straße</t>
+        </is>
+      </c>
+      <c r="H914" s="2" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="I914" s="2" t="inlineStr">
+        <is>
+          <t>https://wine-world.at</t>
+        </is>
+      </c>
+      <c r="J914" s="2" t="inlineStr"/>
+      <c r="K914" s="2" t="inlineStr"/>
+      <c r="L914" s="2" t="inlineStr"/>
+      <c r="M914" s="2" t="inlineStr"/>
+      <c r="N914" s="2" t="inlineStr">
+        <is>
+          <t>orders@wine-world.at</t>
+        </is>
+      </c>
+      <c r="O914" s="2" t="inlineStr"/>
+      <c r="P914" s="2" t="inlineStr"/>
+      <c r="Q914" s="2" t="inlineStr"/>
+      <c r="R914" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wine-world-at/</t>
+        </is>
+      </c>
+      <c r="S914" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/wineworldnew</t>
+        </is>
+      </c>
+      <c r="T914" s="2" t="inlineStr"/>
+      <c r="U914" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/wineworldnew</t>
+        </is>
+      </c>
+      <c r="V914" s="2" t="inlineStr"/>
+      <c r="W914" s="2" t="inlineStr">
+        <is>
+          <t>Katharina Monsberger</t>
+        </is>
+      </c>
+      <c r="X914" s="2" t="inlineStr">
+        <is>
+          <t>Head of Sales</t>
+        </is>
+      </c>
+      <c r="Y914" s="2" t="inlineStr"/>
+      <c r="Z914" s="2" t="inlineStr"/>
+      <c r="AA914" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/katharina-monsberger-bb7bb11a1/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
